--- a/data/Formula_1/F1_2026.xlsx
+++ b/data/Formula_1/F1_2026.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vyan\Documents\GitHub\Formula_1\data\Formula_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFC8C393-DD72-41DC-8C7E-C0E1921672D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11895F56-DCB2-47C8-AF33-282C42F93266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Schedule" sheetId="1" r:id="rId1"/>
     <sheet name="Drivers List" sheetId="2" r:id="rId2"/>
-    <sheet name="Driver Details" sheetId="3" r:id="rId3"/>
+    <sheet name="Teams" sheetId="6" r:id="rId3"/>
+    <sheet name="Driver Details" sheetId="3" r:id="rId4"/>
+    <sheet name="Track Details" sheetId="4" r:id="rId5"/>
+    <sheet name="Team Details" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="207">
   <si>
     <t>Grand Prix</t>
   </si>
@@ -737,12 +740,6 @@
   </si>
   <si>
     <t>Team</t>
-  </si>
-  <si>
-    <t>Driver 1</t>
-  </si>
-  <si>
-    <t>Driver 2</t>
   </si>
   <si>
     <t>McLaren</t>
@@ -937,6 +934,225 @@
   </si>
   <si>
     <t>🇫🇮 Finland</t>
+  </si>
+  <si>
+    <t>Entrant</t>
+  </si>
+  <si>
+    <t>Constructor</t>
+  </si>
+  <si>
+    <t>Chassis</t>
+  </si>
+  <si>
+    <t>Power unit</t>
+  </si>
+  <si>
+    <t>Race drivers</t>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>Driver name</t>
+  </si>
+  <si>
+    <t>France BWT Alpine F1 Team[3]</t>
+  </si>
+  <si>
+    <t>Alpine-Mercedes</t>
+  </si>
+  <si>
+    <t>A526[4]</t>
+  </si>
+  <si>
+    <t>Mercedes-AMG F1 M17[5][6]</t>
+  </si>
+  <si>
+    <t>France Pierre Gasly</t>
+  </si>
+  <si>
+    <t>Argentina Franco Colapinto</t>
+  </si>
+  <si>
+    <t>United Kingdom Aston Martin Aramco F1 Team[7]</t>
+  </si>
+  <si>
+    <t>Aston Martin Aramco-Honda</t>
+  </si>
+  <si>
+    <t>AMR26[8]</t>
+  </si>
+  <si>
+    <t>Honda RA626H[9][10]</t>
+  </si>
+  <si>
+    <t>Spain Fernando Alonso</t>
+  </si>
+  <si>
+    <t>Canada Lance Stroll</t>
+  </si>
+  <si>
+    <t>United Kingdom Atlassian Williams F1 Team[11][12]</t>
+  </si>
+  <si>
+    <t>Atlassian Williams-Mercedes</t>
+  </si>
+  <si>
+    <t>FW48[13]</t>
+  </si>
+  <si>
+    <t>Mercedes-AMG F1 M17[14]</t>
+  </si>
+  <si>
+    <t>Thailand Alexander Albon</t>
+  </si>
+  <si>
+    <t>Spain Carlos Sainz Jr.</t>
+  </si>
+  <si>
+    <t>Germany Audi Revolut F1 Team[15][16][17]</t>
+  </si>
+  <si>
+    <t>R26[18]</t>
+  </si>
+  <si>
+    <t>Audi AFR 26 Hybrid[15]</t>
+  </si>
+  <si>
+    <t>Brazil Gabriel Bortoleto</t>
+  </si>
+  <si>
+    <t>Germany Nico Hülkenberg</t>
+  </si>
+  <si>
+    <t>United States Cadillac Formula 1 Team[19][20][21]</t>
+  </si>
+  <si>
+    <t>Cadillac-Ferrari</t>
+  </si>
+  <si>
+    <t>MAC-26[22]</t>
+  </si>
+  <si>
+    <t>Ferrari 067/6[23]</t>
+  </si>
+  <si>
+    <t>Mexico Sergio Pérez</t>
+  </si>
+  <si>
+    <t>Finland Valtteri Bottas</t>
+  </si>
+  <si>
+    <t>Italy Scuderia Ferrari HP[24]</t>
+  </si>
+  <si>
+    <t>SF-26[25]</t>
+  </si>
+  <si>
+    <t>Ferrari 067/6[26][27]</t>
+  </si>
+  <si>
+    <t>Monaco Charles Leclerc</t>
+  </si>
+  <si>
+    <t>United Kingdom Lewis Hamilton</t>
+  </si>
+  <si>
+    <t>United States TGR Haas F1 Team[28]</t>
+  </si>
+  <si>
+    <t>Haas-Ferrari</t>
+  </si>
+  <si>
+    <t>VF-26[28]</t>
+  </si>
+  <si>
+    <t>Ferrari 067/6[29][30]</t>
+  </si>
+  <si>
+    <t>France Esteban Ocon</t>
+  </si>
+  <si>
+    <t>United Kingdom Oliver Bearman</t>
+  </si>
+  <si>
+    <t>United Kingdom McLaren Mastercard F1 Team[31]</t>
+  </si>
+  <si>
+    <t>McLaren-Mercedes</t>
+  </si>
+  <si>
+    <t>MCL40[32]</t>
+  </si>
+  <si>
+    <t>Mercedes-AMG F1 M17[33]</t>
+  </si>
+  <si>
+    <t>United Kingdom Lando Norris</t>
+  </si>
+  <si>
+    <t>Australia Oscar Piastri</t>
+  </si>
+  <si>
+    <t>Germany Mercedes-AMG Petronas F1 Team[34]</t>
+  </si>
+  <si>
+    <t>F1 W17[35]</t>
+  </si>
+  <si>
+    <t>Mercedes-AMG F1 M17[26]</t>
+  </si>
+  <si>
+    <t> Kimi Antonelli</t>
+  </si>
+  <si>
+    <t> George Russell</t>
+  </si>
+  <si>
+    <t>Italy Visa Cash App Racing Bulls F1 Team[36]</t>
+  </si>
+  <si>
+    <t>Racing Bulls-Red Bull Ford</t>
+  </si>
+  <si>
+    <t>VCARB 03[37]</t>
+  </si>
+  <si>
+    <t>Red Bull Ford DM01[38][39]</t>
+  </si>
+  <si>
+    <t> Liam Lawson</t>
+  </si>
+  <si>
+    <t> Arvid Lindblad</t>
+  </si>
+  <si>
+    <t>Austria Oracle Red Bull Racing[40]</t>
+  </si>
+  <si>
+    <t>Red Bull Racing-Red Bull Ford</t>
+  </si>
+  <si>
+    <t>RB22[41]</t>
+  </si>
+  <si>
+    <t>Red Bull Ford DM01[38][39]</t>
+  </si>
+  <si>
+    <t>Netherlands Max Verstappen</t>
+  </si>
+  <si>
+    <t> Isack Hadjar</t>
+  </si>
+  <si>
+    <t>Sources:[42][43]</t>
+  </si>
+  <si>
+    <t>Teams</t>
+  </si>
+  <si>
+    <t>Audi F1 Team (formerly Sauber)</t>
   </si>
 </sst>
 </file>
@@ -1018,7 +1234,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1057,6 +1273,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1704,7 +1921,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAD59E1D-E68C-4E94-9977-6535F44A6664}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.109375" bestFit="1" customWidth="1"/>
@@ -1717,131 +1934,184 @@
         <v>76</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>78</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="C1" s="10"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A10" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="12" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
+      <c r="B14" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="B3" s="12" t="s">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="B15" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="12" t="s">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
+      <c r="B16" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="B5" s="12" t="s">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="B17" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B6" s="12" t="s">
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
+      <c r="B18" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="B7" s="12" t="s">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+      <c r="B19" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="B8" s="12" t="s">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
+      <c r="B20" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="C9" s="12" t="s">
+    </row>
+    <row r="21" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A21" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="40.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="B10" s="12" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="B22" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="B11" s="12" t="s">
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
+      <c r="B23" s="12" t="s">
         <v>108</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1850,6 +2120,80 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76DC5FB4-477A-4B4C-B4BA-2F7A47B1EF35}">
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr defaultRowHeight="10.199999999999999" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="21.5546875" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="8.88671875" style="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" s="14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" s="14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" s="14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" s="14" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" s="14" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" s="14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A9" s="14" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" s="14" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A11" s="14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A12" s="14" t="s">
+        <v>106</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6195B2D-ED40-4B99-B245-D9B462D3C9B9}">
   <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1862,16 +2206,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -1879,13 +2223,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -1893,13 +2237,13 @@
         <v>81</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1907,13 +2251,13 @@
         <v>63</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1921,13 +2265,13 @@
         <v>12</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -1935,13 +2279,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -1949,13 +2293,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -1963,13 +2307,13 @@
         <v>16</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -1977,13 +2321,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -1991,13 +2335,13 @@
         <v>23</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -2005,13 +2349,13 @@
         <v>55</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -2019,13 +2363,13 @@
         <v>30</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -2033,13 +2377,13 @@
         <v>41</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -2047,13 +2391,13 @@
         <v>14</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -2061,13 +2405,13 @@
         <v>18</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -2075,13 +2419,13 @@
         <v>31</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -2089,13 +2433,13 @@
         <v>87</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -2103,13 +2447,13 @@
         <v>27</v>
       </c>
       <c r="B18" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D18" s="13" t="s">
         <v>128</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -2117,13 +2461,13 @@
         <v>5</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C19" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D19" s="13" t="s">
         <v>129</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -2131,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -2145,13 +2489,13 @@
         <v>43</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -2159,13 +2503,13 @@
         <v>11</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -2173,14 +2517,562 @@
         <v>77</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C23" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D23" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="D23" s="13" t="s">
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAAFE55E-C4A5-441F-855A-F0C6AC6A455A}">
+  <dimension ref="A1:A25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.88671875" style="4" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB0BD2E0-4D0A-4FD2-81AD-FA7EA9E4BE28}">
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="35.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>135</v>
       </c>
+      <c r="C1" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1" s="14"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="E3" s="14">
+        <v>10</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14">
+        <v>43</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="E5" s="14">
+        <v>14</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14">
+        <v>18</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="E7" s="14">
+        <v>23</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14">
+        <v>55</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="E9" s="14">
+        <v>5</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14">
+        <v>27</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="E11" s="14">
+        <v>11</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14">
+        <v>77</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="E13" s="14">
+        <v>16</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14">
+        <v>44</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="E15" s="14">
+        <v>31</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14">
+        <v>87</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="E17" s="14">
+        <v>1</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14">
+        <v>81</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="E19" s="14">
+        <v>12</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14">
+        <v>63</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="E21" s="14">
+        <v>30</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="14"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14">
+        <v>41</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="E23" s="14">
+        <v>3</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="14"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14">
+        <v>6</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Formula_1/F1_2026.xlsx
+++ b/data/Formula_1/F1_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vyan\Documents\GitHub\Formula_1\data\Formula_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11895F56-DCB2-47C8-AF33-282C42F93266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{541C0894-32E2-418B-BECC-4D343A50CC50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Schedule" sheetId="1" r:id="rId1"/>
@@ -1234,7 +1234,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1274,6 +1274,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2129,7 +2130,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>205</v>
       </c>
     </row>
@@ -2200,7 +2201,7 @@
   <cols>
     <col min="1" max="1" width="4.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" customWidth="1"/>
     <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
